--- a/docs/분류규칙_seed_고정지출추가.xlsx
+++ b/docs/분류규칙_seed_고정지출추가.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mrat1765-my.sharepoint.com/personal/yeoheejeong_mrat1765_onmicrosoft_com/Documents/미래.여과장.업무파일.다시정리하자/회사서류/★★개발중/현금흐름관리/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6C683E8-F5FA-4E18-BA88-65708F0E2356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFCC3EF-E609-4680-96CA-866179E51AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{2EA3B530-21F1-4274-8C0A-EFAF3A0C89F2}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{53FEB7AA-5BB0-4313-9C47-34F02023C30C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="64">
   <si>
     <t>사업체</t>
   </si>
@@ -59,10 +59,13 @@
     <t>결제예정일</t>
   </si>
   <si>
+    <t>고정분류</t>
+  </si>
+  <si>
+    <t>예정금액</t>
+  </si>
+  <si>
     <t>우선순위</t>
-  </si>
-  <si>
-    <t>고정분류</t>
   </si>
   <si>
     <t>엠오토</t>
@@ -610,11 +613,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172B3527-B37C-4277-867D-013A4709E28F}">
-  <dimension ref="A1:H37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36076D4E-EBD8-4D2C-AFBB-ACBE4937A3CE}">
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -639,854 +642,926 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>92741601415310</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2">
+        <v>200000</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3">
+        <v>20000</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4">
+        <v>20000</v>
+      </c>
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>250000</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>7</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>2000000</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
       </c>
       <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>2000000</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>92741601435024</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>8</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>150000</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>92741601306726</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>10</v>
       </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10">
+        <v>1350000</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>92741601487768</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11">
         <v>10</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>1350000</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12">
+        <v>200000</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
         <v>30</v>
       </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="E13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13">
+      <c r="H13">
+        <v>200000</v>
+      </c>
+      <c r="I13">
         <v>2</v>
       </c>
-      <c r="H13" t="s">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
       <c r="F14">
         <v>10</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14">
+        <v>110000</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>92741601531533</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>15</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>300000</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>92741601531520</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16">
         <v>15</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16">
+        <v>300000</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17">
         <v>21</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17">
+        <v>100000</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F18">
         <v>21</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18">
+        <v>90000</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19">
         <v>21</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="G19" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19">
+        <v>170000</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F20">
         <v>21</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20">
+        <v>170000</v>
+      </c>
+      <c r="I20">
         <v>2</v>
       </c>
-      <c r="H20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21">
         <v>102024</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21">
         <v>21</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21">
+        <v>170000</v>
+      </c>
+      <c r="I21">
         <v>2</v>
       </c>
-      <c r="H21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <v>3332043328917</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22">
         <v>23</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <v>2500000</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23">
         <v>3332043328917</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23">
         <v>23</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>2500000</v>
+      </c>
+      <c r="I23">
         <v>2</v>
       </c>
-      <c r="H23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24">
         <v>23</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
         <v>46</v>
-      </c>
-      <c r="D25" t="s">
-        <v>45</v>
       </c>
       <c r="F25">
         <v>23</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26">
         <v>23</v>
       </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F27">
         <v>23</v>
       </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28">
         <v>23</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28">
         <v>2</v>
       </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F29">
         <v>25</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29">
         <v>2</v>
       </c>
-      <c r="H29" t="s">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" t="s">
-        <v>50</v>
-      </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30">
         <v>25</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30">
         <v>2</v>
       </c>
-      <c r="H30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>92741601394266</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F31">
         <v>25</v>
       </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31">
+        <v>300000</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32">
         <v>25</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32">
+        <v>31900</v>
+      </c>
+      <c r="I32">
         <v>2</v>
       </c>
-      <c r="H32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F33">
         <v>26</v>
       </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F34">
         <v>30</v>
       </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F35">
         <v>31</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35">
         <v>2</v>
       </c>
-      <c r="H35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F36">
         <v>31</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36">
         <v>2</v>
       </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
         <v>3</v>
       </c>
       <c r="C37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" t="s">
         <v>62</v>
-      </c>
-      <c r="D37" t="s">
-        <v>61</v>
       </c>
       <c r="F37">
         <v>31</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37">
         <v>3</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
